--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -49935,7 +49935,7 @@
       </c>
       <c r="G1003" s="3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H1003" s="5" t="n">
@@ -52339,7 +52339,7 @@
       </c>
       <c r="G1055" s="3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H1055" s="5" t="n">
@@ -64650,7 +64650,7 @@
           <t>G | 306呎 (1房)
 $579万
 $18,915/呎
-(26年-04月)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
@@ -65094,7 +65094,7 @@
           <t>G | 306呎 (1房)
 $572万
 $18,686/呎
-(26年-04月)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -43490,7 +43490,7 @@
       </c>
       <c r="G863" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H863" s="5" t="n">
@@ -53853,27 +53853,23 @@
       </c>
       <c r="F1087" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1087" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H1087" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I1087" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H1087" s="5" t="n">
+        <v>13768000</v>
+      </c>
+      <c r="I1087" s="5" t="n">
+        <v>22460</v>
       </c>
       <c r="J1087" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -62540,7 +62536,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -62550,7 +62546,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>271</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -63448,7 +63444,7 @@
           <t>D | 432呎 (2房)
 $1063万
 $24,597/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -65306,12 +65302,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 613呎 (2房)
-招标单位
--
-(在售)</t>
+$1377万
+$22,460/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -72044,7 +72044,7 @@
       </c>
       <c r="G1048" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H1048" s="5" t="n">
@@ -86230,7 +86230,7 @@
           <t>A | 613呎 (2房)
 $1430万
 $23,328/呎
-(26年-06月-15日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -70969,23 +70969,23 @@
       </c>
       <c r="F1031" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G1031" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H1031" s="5" t="n">
-        <v>15080000</v>
+        <v>11310000</v>
       </c>
       <c r="I1031" s="5" t="n">
-        <v>30220</v>
+        <v>22665</v>
       </c>
       <c r="J1031" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K1031" s="5" t="n">
@@ -70996,7 +70996,7 @@
       </c>
       <c r="M1031" s="3" t="inlineStr">
         <is>
-          <t>置輕鬆置簡單120天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N1031" s="3" t="inlineStr">
@@ -83792,7 +83792,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -83802,7 +83802,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -86146,12 +86146,12 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1508万
-$30,220/呎
-(在售)</t>
+$1131万
+$22,665/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">

--- a/files/九龙-启德-启德海湾 2.xlsx
+++ b/files/九龙-启德-启德海湾 2.xlsx
@@ -84169,7 +84169,7 @@
           <t>K | 426呎 (2房)
 $1022万
 $24,002/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr">
@@ -84177,7 +84177,7 @@
           <t>L | 305呎 (1房)
 $732万
 $24,000/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -84248,7 +84248,7 @@
           <t>F | 307呎 (1房)
 $658万
 $21,417/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -84256,7 +84256,7 @@
           <t>G | 306呎 (1房)
 $658万
 $21,490/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -84264,7 +84264,7 @@
           <t>H | 306呎 (1房)
 $660万
 $21,556/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="J8" s="23" t="inlineStr">
@@ -84272,7 +84272,7 @@
           <t>J | 308呎 (1房)
 $664万
 $21,552/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K8" s="23" t="inlineStr">
@@ -84280,7 +84280,7 @@
           <t>K | 426呎 (2房)
 $908万
 $21,319/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L8" s="23" t="inlineStr">
@@ -84288,7 +84288,7 @@
           <t>L | 305呎 (1房)
 $679万
 $22,269/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -84359,7 +84359,7 @@
           <t>F | 307呎 (1房)
 $651万
 $21,205/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -84367,7 +84367,7 @@
           <t>G | 306呎 (1房)
 $651万
 $21,275/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -84375,7 +84375,7 @@
           <t>H | 306呎 (1房)
 $653万
 $21,346/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -84383,7 +84383,7 @@
           <t>J | 308呎 (1房)
 $658万
 $21,347/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K9" s="23" t="inlineStr">
@@ -84391,7 +84391,7 @@
           <t>K | 426呎 (2房)
 $899万
 $21,108/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr">
@@ -84399,7 +84399,7 @@
           <t>L | 305呎 (1房)
 $672万
 $22,049/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="M9" s="23" t="inlineStr">
@@ -84407,7 +84407,7 @@
           <t>M | 429呎 (2房)
 $994万
 $23,166/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="N9" s="23" t="inlineStr">
@@ -84415,7 +84415,7 @@
           <t>N | 278呎 (1房)
 $664万
 $23,892/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -84470,7 +84470,7 @@
           <t>F | 307呎 (1房)
 $644万
 $20,993/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -84478,7 +84478,7 @@
           <t>G | 306呎 (1房)
 $644万
 $21,056/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -84486,7 +84486,7 @@
           <t>H | 306呎 (1房)
 $647万
 $21,137/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -84494,7 +84494,7 @@
           <t>J | 308呎 (1房)
 $651万
 $21,136/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="K10" s="23" t="inlineStr">
@@ -84502,7 +84502,7 @@
           <t>K | 426呎 (2房)
 $891万
 $20,906/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L10" s="23" t="inlineStr">
@@ -84510,7 +84510,7 @@
           <t>L | 305呎 (1房)
 $666万
 $21,830/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
@@ -84518,7 +84518,7 @@
           <t>M | 429呎 (2房)
 $951万
 $22,159/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="N10" s="23" t="inlineStr">
@@ -84526,7 +84526,7 @@
           <t>N | 278呎 (1房)
 $638万
 $22,964/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -84581,7 +84581,7 @@
           <t>F | 307呎 (1房)
 $638万
 $20,782/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -84589,7 +84589,7 @@
           <t>G | 306呎 (1房)
 $638万
 $20,850/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -84597,7 +84597,7 @@
           <t>H | 306呎 (1房)
 $641万
 $20,935/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -84605,7 +84605,7 @@
           <t>J | 308呎 (1房)
 $645万
 $20,929/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -84613,7 +84613,7 @@
           <t>K | 426呎 (2房)
 $882万
 $20,692/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L11" s="23" t="inlineStr">
@@ -84621,7 +84621,7 @@
           <t>L | 305呎 (1房)
 $659万
 $21,613/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="M11" s="23" t="inlineStr">
@@ -84629,7 +84629,7 @@
           <t>M | 429呎 (2房)
 $941万
 $21,939/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N11" s="23" t="inlineStr">
@@ -84637,7 +84637,7 @@
           <t>N | 278呎 (1房)
 $632万
 $22,737/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -84652,7 +84652,7 @@
           <t>A | 613呎 (2房)
 $1566万
 $25,540/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -84660,7 +84660,7 @@
           <t>B | 486呎 (2房)
 $1217万
 $25,035/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -84668,7 +84668,7 @@
           <t>C | 548呎 (2房)
 $1330万
 $24,279/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -84676,7 +84676,7 @@
           <t>D | 432呎 (2房)
 $1063万
 $24,597/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -84684,7 +84684,7 @@
           <t>E | 499呎 (2房)
 $1213万
 $24,305/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -84692,7 +84692,7 @@
           <t>F | 307呎 (1房)
 $620万
 $20,189/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -84700,7 +84700,7 @@
           <t>G | 306呎 (1房)
 $620万
 $20,255/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -84708,7 +84708,7 @@
           <t>H | 306呎 (1房)
 $622万
 $20,310/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -84716,7 +84716,7 @@
           <t>J | 308呎 (1房)
 $626万
 $20,308/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -84724,7 +84724,7 @@
           <t>K | 426呎 (2房)
 $856万
 $20,099/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="L12" s="23" t="inlineStr">
@@ -84732,7 +84732,7 @@
           <t>L | 305呎 (1房)
 $665万
 $21,816/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -84740,7 +84740,7 @@
           <t>M | 429呎 (2房)
 $913万
 $21,287/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N12" s="23" t="inlineStr">
@@ -84748,7 +84748,7 @@
           <t>N | 278呎 (1房)
 $614万
 $22,068/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -84763,7 +84763,7 @@
           <t>A | 613呎 (2房)
 $1476万
 $24,078/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -84771,7 +84771,7 @@
           <t>B | 486呎 (2房)
 $1158万
 $23,831/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -84779,7 +84779,7 @@
           <t>C | 548呎 (2房)
 $1317万
 $24,038/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -84795,7 +84795,7 @@
           <t>E | 499呎 (2房)
 $1172万
 $23,477/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -84803,7 +84803,7 @@
           <t>F | 307呎 (1房)
 $613万
 $19,977/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -84811,7 +84811,7 @@
           <t>G | 306呎 (1房)
 $613万
 $20,042/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -84819,7 +84819,7 @@
           <t>H | 306呎 (1房)
 $615万
 $20,108/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -84827,7 +84827,7 @@
           <t>J | 308呎 (1房)
 $620万
 $20,117/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr">
@@ -84835,7 +84835,7 @@
           <t>K | 426呎 (2房)
 $847万
 $19,887/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L13" s="23" t="inlineStr">
@@ -84843,7 +84843,7 @@
           <t>L | 305呎 (1房)
 $634万
 $20,770/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -84851,7 +84851,7 @@
           <t>M | 429呎 (2房)
 $941万
 $21,928/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N13" s="23" t="inlineStr">
@@ -84859,7 +84859,7 @@
           <t>N | 278呎 (1房)
 $608万
 $21,863/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -84890,7 +84890,7 @@
           <t>C | 548呎 (2房)
 $1399万
 $25,526/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -84914,7 +84914,7 @@
           <t>F | 307呎 (1房)
 $607万
 $19,772/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -84922,7 +84922,7 @@
           <t>G | 306呎 (1房)
 $607万
 $19,837/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -84930,7 +84930,7 @@
           <t>H | 306呎 (1房)
 $609万
 $19,908/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -84938,7 +84938,7 @@
           <t>J | 308呎 (1房)
 $638万
 $20,708/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr">
@@ -84946,7 +84946,7 @@
           <t>K | 426呎 (2房)
 $839万
 $19,690/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L14" s="23" t="inlineStr">
@@ -84954,7 +84954,7 @@
           <t>L | 305呎 (1房)
 $628万
 $20,577/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -84962,7 +84962,7 @@
           <t>M | 429呎 (2房)
 $896万
 $20,876/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N14" s="23" t="inlineStr">
@@ -84970,7 +84970,7 @@
           <t>N | 278呎 (1房)
 $614万
 $22,068/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -84985,7 +84985,7 @@
           <t>A | 613呎 (2房)
 $1534万
 $25,021/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -85001,7 +85001,7 @@
           <t>C | 548呎 (2房)
 $1369万
 $24,978/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -85025,7 +85025,7 @@
           <t>F | 307呎 (1房)
 $601万
 $19,577/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -85033,7 +85033,7 @@
           <t>G | 306呎 (1房)
 $601万
 $19,641/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -85041,7 +85041,7 @@
           <t>H | 306呎 (1房)
 $603万
 $19,712/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -85049,7 +85049,7 @@
           <t>J | 308呎 (1房)
 $608万
 $19,727/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr">
@@ -85057,7 +85057,7 @@
           <t>K | 426呎 (2房)
 $830万
 $19,495/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="L15" s="23" t="inlineStr">
@@ -85065,7 +85065,7 @@
           <t>L | 305呎 (1房)
 $621万
 $20,367/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M15" s="23" t="inlineStr">
@@ -85073,7 +85073,7 @@
           <t>M | 429呎 (2房)
 $887万
 $20,667/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N15" s="23" t="inlineStr">
@@ -85081,7 +85081,7 @@
           <t>N | 278呎 (1房)
 $596万
 $21,421/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -85096,7 +85096,7 @@
           <t>A | 613呎 (2房)
 $1433万
 $23,370/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -85104,7 +85104,7 @@
           <t>B | 486呎 (2房)
 $1124万
 $23,132/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -85112,7 +85112,7 @@
           <t>C | 548呎 (2房)
 $1278万
 $23,330/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -85120,7 +85120,7 @@
           <t>D | 432呎 (2房)
 $1001万
 $23,167/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -85128,7 +85128,7 @@
           <t>E | 499呎 (2房)
 $1137万
 $22,786/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -85136,7 +85136,7 @@
           <t>F | 307呎 (1房)
 $595万
 $19,388/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -85144,7 +85144,7 @@
           <t>G | 306呎 (1房)
 $595万
 $19,451/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -85152,7 +85152,7 @@
           <t>H | 306呎 (1房)
 $597万
 $19,516/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -85160,7 +85160,7 @@
           <t>J | 308呎 (1房)
 $601万
 $19,506/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -85168,7 +85168,7 @@
           <t>K | 426呎 (2房)
 $822万
 $19,308/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
@@ -85176,7 +85176,7 @@
           <t>L | 305呎 (1房)
 $615万
 $20,170/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
@@ -85184,7 +85184,7 @@
           <t>M | 429呎 (2房)
 $878万
 $20,462/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N16" s="23" t="inlineStr">
@@ -85192,7 +85192,7 @@
           <t>N | 278呎 (1房)
 $590万
 $21,216/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -85207,7 +85207,7 @@
           <t>A | 613呎 (2房)
 $1426万
 $23,263/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -85215,7 +85215,7 @@
           <t>B | 486呎 (2房)
 $1119万
 $23,016/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -85223,7 +85223,7 @@
           <t>C | 548呎 (2房)
 $1272万
 $23,215/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -85231,7 +85231,7 @@
           <t>D | 432呎 (2房)
 $996万
 $23,056/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -85239,7 +85239,7 @@
           <t>E | 499呎 (2房)
 $1177万
 $23,583/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -85247,7 +85247,7 @@
           <t>F | 307呎 (1房)
 $593万
 $19,326/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -85255,7 +85255,7 @@
           <t>G | 306呎 (1房)
 $593万
 $19,389/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -85263,7 +85263,7 @@
           <t>H | 306呎 (1房)
 $596万
 $19,461/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -85271,7 +85271,7 @@
           <t>J | 308呎 (1房)
 $600万
 $19,464/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -85279,7 +85279,7 @@
           <t>K | 426呎 (2房)
 $820万
 $19,249/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -85287,7 +85287,7 @@
           <t>L | 305呎 (1房)
 $613万
 $20,105/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -85295,7 +85295,7 @@
           <t>M | 429呎 (2房)
 $875万
 $20,401/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N17" s="23" t="inlineStr">
@@ -85303,7 +85303,7 @@
           <t>N | 278呎 (1房)
 $587万
 $21,101/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -85318,7 +85318,7 @@
           <t>A | 613呎 (2房)
 $1418万
 $23,132/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -85326,7 +85326,7 @@
           <t>B | 486呎 (2房)
 $1113万
 $22,901/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -85334,7 +85334,7 @@
           <t>C | 548呎 (2房)
 $1266万
 $23,099/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -85342,7 +85342,7 @@
           <t>D | 432呎 (2房)
 $991万
 $22,940/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -85350,7 +85350,7 @@
           <t>E | 499呎 (2房)
 $1126万
 $22,557/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -85358,7 +85358,7 @@
           <t>F | 307呎 (1房)
 $592万
 $19,267/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -85366,7 +85366,7 @@
           <t>G | 306呎 (1房)
 $592万
 $19,330/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -85374,7 +85374,7 @@
           <t>H | 306呎 (1房)
 $594万
 $19,405/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
@@ -85382,7 +85382,7 @@
           <t>J | 308呎 (1房)
 $598万
 $19,399/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
@@ -85390,7 +85390,7 @@
           <t>K | 426呎 (2房)
 $818万
 $19,190/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -85398,7 +85398,7 @@
           <t>L | 305呎 (1房)
 $611万
 $20,039/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M18" s="23" t="inlineStr">
@@ -85406,7 +85406,7 @@
           <t>M | 429呎 (2房)
 $873万
 $20,340/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N18" s="23" t="inlineStr">
@@ -85414,7 +85414,7 @@
           <t>N | 278呎 (1房)
 $584万
 $21,000/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -85429,7 +85429,7 @@
           <t>A | 613呎 (2房)
 $1440万
 $23,488/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -85437,7 +85437,7 @@
           <t>B | 486呎 (2房)
 $1143万
 $23,514/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -85445,7 +85445,7 @@
           <t>C | 548呎 (2房)
 $1285万
 $23,445/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -85453,7 +85453,7 @@
           <t>D | 432呎 (2房)
 $1016万
 $23,523/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -85461,7 +85461,7 @@
           <t>E | 499呎 (2房)
 $1149万
 $23,022/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -85469,7 +85469,7 @@
           <t>F | 307呎 (1房)
 $608万
 $19,792/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -85477,7 +85477,7 @@
           <t>G | 306呎 (1房)
 $608万
 $19,856/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -85485,7 +85485,7 @@
           <t>H | 306呎 (1房)
 $610万
 $19,928/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
@@ -85493,7 +85493,7 @@
           <t>J | 308呎 (1房)
 $614万
 $19,929/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
@@ -85501,7 +85501,7 @@
           <t>K | 426呎 (2房)
 $844万
 $19,808/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
@@ -85509,7 +85509,7 @@
           <t>L | 305呎 (1房)
 $628万
 $20,584/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M19" s="23" t="inlineStr">
@@ -85517,7 +85517,7 @@
           <t>M | 429呎 (2房)
 $901万
 $20,998/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="N19" s="23" t="inlineStr">
@@ -85525,7 +85525,7 @@
           <t>N | 278呎 (1房)
 $599万
 $21,540/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -85580,7 +85580,7 @@
           <t>F | 307呎 (1房)
 $606万
 $19,739/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -85588,7 +85588,7 @@
           <t>G | 306呎 (1房)
 $606万
 $19,791/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -85596,7 +85596,7 @@
           <t>H | 306呎 (1房)
 $608万
 $19,863/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -85604,7 +85604,7 @@
           <t>J | 308呎 (1房)
 $612万
 $19,864/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr">
@@ -85612,7 +85612,7 @@
           <t>K | 426呎 (2房)
 $842万
 $19,761/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
@@ -85620,7 +85620,7 @@
           <t>L | 305呎 (1房)
 $626万
 $20,525/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="M20" s="23" t="inlineStr">
@@ -85628,7 +85628,7 @@
           <t>M | 429呎 (2房)
 $899万
 $20,951/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="N20" s="23" t="inlineStr">
@@ -85636,7 +85636,7 @@
           <t>N | 278呎 (1房)
 $595万
 $21,410/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -85651,7 +85651,7 @@
           <t>A | 613呎 (2房)
 $1445万
 $23,579/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -85659,7 +85659,7 @@
           <t>B | 486呎 (2房)
 $1091万
 $22,449/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -85667,7 +85667,7 @@
           <t>C | 548呎 (2房)
 $1240万
 $22,620/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -85675,7 +85675,7 @@
           <t>D | 432呎 (2房)
 $972万
 $22,491/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -85683,7 +85683,7 @@
           <t>E | 499呎 (2房)
 $1149万
 $23,022/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -85691,7 +85691,7 @@
           <t>F | 307呎 (1房)
 $582万
 $18,967/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -85699,7 +85699,7 @@
           <t>G | 306呎 (1房)
 $606万
 $19,791/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -85707,7 +85707,7 @@
           <t>H | 306呎 (1房)
 $584万
 $19,101/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -85715,7 +85715,7 @@
           <t>J | 308呎 (1房)
 $588万
 $19,097/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr">
@@ -85723,7 +85723,7 @@
           <t>K | 426呎 (2房)
 $804万
 $18,885/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -85731,7 +85731,7 @@
           <t>L | 305呎 (1房)
 $602万
 $19,725/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M21" s="23" t="inlineStr">
@@ -85739,7 +85739,7 @@
           <t>M | 429呎 (2房)
 $893万
 $20,818/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="N21" s="23" t="inlineStr">
@@ -85747,7 +85747,7 @@
           <t>N | 278呎 (1房)
 $590万
 $21,205/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -85762,7 +85762,7 @@
           <t>A | 613呎 (2房)
 $1438万
 $23,460/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -85770,7 +85770,7 @@
           <t>B | 486呎 (2房)
 $1087万
 $22,358/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -85778,7 +85778,7 @@
           <t>C | 548呎 (2房)
 $1235万
 $22,536/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -85786,7 +85786,7 @@
           <t>D | 432呎 (2房)
 $967万
 $22,380/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -85794,7 +85794,7 @@
           <t>E | 499呎 (2房)
 $1098万
 $22,000/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -85802,7 +85802,7 @@
           <t>F | 307呎 (1房)
 $580万
 $18,909/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -85810,7 +85810,7 @@
           <t>G | 306呎 (1房)
 $580万
 $18,971/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -85818,7 +85818,7 @@
           <t>H | 306呎 (1房)
 $582万
 $19,036/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -85826,7 +85826,7 @@
           <t>J | 308呎 (1房)
 $587万
 $19,052/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
@@ -85834,7 +85834,7 @@
           <t>K | 426呎 (2房)
 $802万
 $18,826/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -85842,7 +85842,7 @@
           <t>L | 305呎 (1房)
 $600万
 $19,666/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -85850,7 +85850,7 @@
           <t>M | 429呎 (2房)
 $856万
 $19,958/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N22" s="23" t="inlineStr">
@@ -85858,7 +85858,7 @@
           <t>N | 278呎 (1房)
 $570万
 $20,486/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -85873,7 +85873,7 @@
           <t>A | 613呎 (2房)
 $1376万
 $22,447/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -85881,7 +85881,7 @@
           <t>B | 486呎 (2房)
 $1080万
 $22,222/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -85889,7 +85889,7 @@
           <t>C | 548呎 (2房)
 $1228万
 $22,412/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -85897,7 +85897,7 @@
           <t>D | 432呎 (2房)
 $962万
 $22,264/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -85913,7 +85913,7 @@
           <t>F | 307呎 (1房)
 $579万
 $18,853/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -85921,7 +85921,7 @@
           <t>G | 306呎 (1房)
 $579万
 $18,915/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -85929,7 +85929,7 @@
           <t>H | 306呎 (1房)
 $581万
 $18,980/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -85937,7 +85937,7 @@
           <t>J | 308呎 (1房)
 $585万
 $18,981/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K23" s="23" t="inlineStr">
@@ -85945,7 +85945,7 @@
           <t>K | 426呎 (2房)
 $800万
 $18,775/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L23" s="23" t="inlineStr">
@@ -85953,7 +85953,7 @@
           <t>L | 305呎 (1房)
 $598万
 $19,607/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="M23" s="23" t="inlineStr">
@@ -85961,7 +85961,7 @@
           <t>M | 429呎 (2房)
 $854万
 $19,900/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="N23" s="23" t="inlineStr">
@@ -85969,7 +85969,7 @@
           <t>N | 278呎 (1房)
 $584万
 $20,989/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -85984,7 +85984,7 @@
           <t>A | 613呎 (2房)
 $1369万
 $22,336/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -85992,7 +85992,7 @@
           <t>B | 486呎 (2房)
 $1075万
 $22,111/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -86000,7 +86000,7 @@
           <t>C | 548呎 (2房)
 $1222万
 $22,301/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -86008,7 +86008,7 @@
           <t>D | 432呎 (2房)
 $957万
 $22,148/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -86016,7 +86016,7 @@
           <t>E | 499呎 (2房)
 $1087万
 $21,780/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -86024,7 +86024,7 @@
           <t>F | 307呎 (1房)
 $577万
 $18,795/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -86032,7 +86032,7 @@
           <t>G | 306呎 (1房)
 $577万
 $18,856/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -86040,7 +86040,7 @@
           <t>H | 306呎 (1房)
 $579万
 $18,928/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -86048,7 +86048,7 @@
           <t>J | 308呎 (1房)
 $583万
 $18,922/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -86056,7 +86056,7 @@
           <t>K | 426呎 (2房)
 $798万
 $18,721/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -86064,7 +86064,7 @@
           <t>L | 305呎 (1房)
 $596万
 $19,548/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M24" s="23" t="inlineStr">
@@ -86072,7 +86072,7 @@
           <t>M | 429呎 (2房)
 $851万
 $19,837/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N24" s="23" t="inlineStr">
@@ -86080,7 +86080,7 @@
           <t>N | 278呎 (1房)
 $564万
 $20,273/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -86095,7 +86095,7 @@
           <t>A | 613呎 (2房)
 $1390万
 $22,672/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -86103,7 +86103,7 @@
           <t>B | 486呎 (2房)
 $1108万
 $22,798/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -86111,7 +86111,7 @@
           <t>C | 548呎 (2房)
 $1241万
 $22,642/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -86119,7 +86119,7 @@
           <t>D | 432呎 (2房)
 $971万
 $22,481/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -86127,7 +86127,7 @@
           <t>E | 499呎 (2房)
 $1131万
 $22,665/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -86135,7 +86135,7 @@
           <t>F | 307呎 (1房)
 $593万
 $19,309/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -86143,7 +86143,7 @@
           <t>G | 306呎 (1房)
 $593万
 $19,373/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -86151,7 +86151,7 @@
           <t>H | 306呎 (1房)
 $595万
 $19,431/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -86159,7 +86159,7 @@
           <t>J | 308呎 (1房)
 $599万
 $19,435/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr">
@@ -86167,7 +86167,7 @@
           <t>K | 426呎 (2房)
 $824万
 $19,338/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -86175,7 +86175,7 @@
           <t>L | 305呎 (1房)
 $612万
 $20,072/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M25" s="23" t="inlineStr">
@@ -86183,7 +86183,7 @@
           <t>M | 429呎 (2房)
 $879万
 $20,485/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="N25" s="23" t="inlineStr">
@@ -86191,7 +86191,7 @@
           <t>N | 278呎 (1房)
 $581万
 $20,892/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -86206,7 +86206,7 @@
           <t>A | 613呎 (2房)
 $1430万
 $23,328/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -86214,7 +86214,7 @@
           <t>B | 486呎 (2房)
 $1123万
 $23,103/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -86222,7 +86222,7 @@
           <t>C | 548呎 (2房)
 $1269万
 $23,153/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -86246,7 +86246,7 @@
           <t>F | 307呎 (1房)
 $591万
 $19,251/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
@@ -86254,7 +86254,7 @@
           <t>G | 306呎 (1房)
 $591万
 $19,307/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -86262,7 +86262,7 @@
           <t>H | 306呎 (1房)
 $593万
 $19,379/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -86270,7 +86270,7 @@
           <t>J | 308呎 (1房)
 $597万
 $19,377/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -86278,7 +86278,7 @@
           <t>K | 426呎 (2房)
 $821万
 $19,268/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -86286,7 +86286,7 @@
           <t>L | 305呎 (1房)
 $611万
 $20,020/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
@@ -86294,7 +86294,7 @@
           <t>M | 429呎 (2房)
 $877万
 $20,438/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N26" s="23" t="inlineStr">
@@ -86302,7 +86302,7 @@
           <t>N | 278呎 (1房)
 $578万
 $20,773/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -86317,7 +86317,7 @@
           <t>A | 613呎 (2房)
 $1336万
 $21,786/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -86325,7 +86325,7 @@
           <t>B | 486呎 (2房)
 $1048万
 $21,570/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -86333,7 +86333,7 @@
           <t>C | 548呎 (2房)
 $1174万
 $21,432/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -86341,7 +86341,7 @@
           <t>D | 432呎 (2房)
 $920万
 $21,292/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -86349,7 +86349,7 @@
           <t>E | 499呎 (2房)
 $1081万
 $21,659/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -86357,7 +86357,7 @@
           <t>F | 307呎 (1房)
 $572万
 $18,625/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
@@ -86365,7 +86365,7 @@
           <t>G | 306呎 (1房)
 $572万
 $18,686/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -86373,7 +86373,7 @@
           <t>H | 306呎 (1房)
 $574万
 $18,752/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -86381,7 +86381,7 @@
           <t>J | 308呎 (1房)
 $578万
 $18,753/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr">
@@ -86389,7 +86389,7 @@
           <t>K | 426呎 (2房)
 $790万
 $18,549/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -86397,7 +86397,7 @@
           <t>L | 305呎 (1房)
 $591万
 $19,370/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="M27" s="23" t="inlineStr">
@@ -86405,7 +86405,7 @@
           <t>M | 429呎 (2房)
 $844万
 $19,662/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="N27" s="23" t="inlineStr">
@@ -86413,7 +86413,7 @@
           <t>N | 278呎 (1房)
 $574万
 $20,640/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -86428,7 +86428,7 @@
           <t>A | 613呎 (2房)
 $1349万
 $22,003/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -86436,7 +86436,7 @@
           <t>B | 486呎 (2房)
 $1068万
 $21,975/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -86444,7 +86444,7 @@
           <t>C | 548呎 (2房)
 $1180万
 $21,533/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -86452,7 +86452,7 @@
           <t>D | 432呎 (2房)
 $906万
 $20,972/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -86460,7 +86460,7 @@
           <t>E | 499呎 (2房)
 $1047万
 $20,978/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -86468,7 +86468,7 @@
           <t>F | 307呎 (1房)
 $569万
 $18,541/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -86476,7 +86476,7 @@
           <t>G | 306呎 (1房)
 $569万
 $18,601/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -86484,7 +86484,7 @@
           <t>H | 306呎 (1房)
 $571万
 $18,660/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -86492,7 +86492,7 @@
           <t>J | 308呎 (1房)
 $575万
 $18,662/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr">
@@ -86500,7 +86500,7 @@
           <t>K | 426呎 (2房)
 $786万
 $18,455/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L28" s="23" t="inlineStr">
@@ -86508,7 +86508,7 @@
           <t>L | 305呎 (1房)
 $588万
 $19,272/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M28" s="23" t="inlineStr">
@@ -86516,7 +86516,7 @@
           <t>M | 429呎 (2房)
 $839万
 $19,562/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="N28" s="23" t="inlineStr">
@@ -86524,7 +86524,7 @@
           <t>N | 278呎 (1房)
 $570万
 $20,486/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -86539,7 +86539,7 @@
           <t>A | 613呎 (2房)
 $1377万
 $22,460/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -86547,7 +86547,7 @@
           <t>B | 486呎 (2房)
 $1081万
 $22,239/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -86555,7 +86555,7 @@
           <t>C | 548呎 (2房)
 $1207万
 $22,022/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
@@ -86563,7 +86563,7 @@
           <t>D | 432呎 (2房)
 $888万
 $20,562/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -86579,7 +86579,7 @@
           <t>F | 307呎 (1房)
 $564万
 $18,355/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -86587,7 +86587,7 @@
           <t>G | 306呎 (1房)
 $564万
 $18,415/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -86595,7 +86595,7 @@
           <t>H | 306呎 (1房)
 $566万
 $18,480/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -86603,7 +86603,7 @@
           <t>J | 308呎 (1房)
 $569万
 $18,481/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
@@ -86611,7 +86611,7 @@
           <t>K | 426呎 (2房)
 $779万
 $18,282/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="L29" s="23" t="inlineStr">
@@ -86619,7 +86619,7 @@
           <t>L | 305呎 (1房)
 $582万
 $19,089/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="M29" s="23" t="inlineStr">
@@ -86627,7 +86627,7 @@
           <t>M | 429呎 (2房)
 $831万
 $19,375/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N29" s="23" t="inlineStr">
@@ -86635,7 +86635,7 @@
           <t>N | 278呎 (1房)
 $565万
 $20,317/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -86666,7 +86666,7 @@
           <t>C | 548呎 (2房)
 $1209万
 $22,058/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -86674,7 +86674,7 @@
           <t>D | 432呎 (2房)
 $843万
 $19,505/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -86682,7 +86682,7 @@
           <t>E | 443呎 (2房)
 $807万
 $18,212/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -86690,7 +86690,7 @@
           <t>F | 307呎 (1房)
 $583万
 $18,990/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -86698,7 +86698,7 @@
           <t>G | 306呎 (1房)
 $560万
 $18,301/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -86706,7 +86706,7 @@
           <t>H | 306呎 (1房)
 $563万
 $18,386/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -86714,7 +86714,7 @@
           <t>J | 308呎 (1房)
 $566万
 $18,383/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -86722,7 +86722,7 @@
           <t>K | 426呎 (2房)
 $775万
 $18,192/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -86730,7 +86730,7 @@
           <t>L | 305呎 (1房)
 $579万
 $18,990/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="M30" s="23" t="inlineStr">
@@ -86738,7 +86738,7 @@
           <t>M | 429呎 (2房)
 $823万
 $19,179/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="N30" s="23" t="inlineStr">
@@ -86746,7 +86746,7 @@
           <t>N | 278呎 (1房)
 $563万
 $20,245/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -86761,7 +86761,7 @@
           <t>A | 613呎 (2房)
 $1326万
 $21,631/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -86769,7 +86769,7 @@
           <t>B | 486呎 (2房)
 $1041万
 $21,416/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -86777,7 +86777,7 @@
           <t>C | 548呎 (2房)
 $1159万
 $21,146/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -86785,7 +86785,7 @@
           <t>D | 432呎 (2房)
 $821万
 $19,000/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -86793,7 +86793,7 @@
           <t>E | 443呎 (2房)
 $799万
 $18,032/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -86801,7 +86801,7 @@
           <t>F | 307呎 (1房)
 $569万
 $18,541/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -86809,7 +86809,7 @@
           <t>G | 306呎 (1房)
 $569万
 $18,601/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -86817,7 +86817,7 @@
           <t>H | 306呎 (1房)
 $571万
 $18,660/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -86825,7 +86825,7 @@
           <t>J | 308呎 (1房)
 $575万
 $18,662/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
@@ -86833,7 +86833,7 @@
           <t>K | 426呎 (2房)
 $786万
 $18,455/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -86841,7 +86841,7 @@
           <t>L | 305呎 (1房)
 $588万
 $19,272/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="M31" s="23" t="inlineStr">
@@ -86849,7 +86849,7 @@
           <t>M | 429呎 (2房)
 $839万
 $19,562/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -86857,7 +86857,7 @@
           <t>N | 278呎 (1房)
 $561万
 $20,173/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -86880,7 +86880,7 @@
           <t>B | 486呎 (2房)
 $1050万
 $21,601/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -86888,7 +86888,7 @@
           <t>C | 550呎 (2房)
 $1178万
 $21,418/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr"/>
